--- a/data/master_data.xlsx
+++ b/data/master_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\68766\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB2CEA51-3674-4B97-8298-250F2BA1E595}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF5321DA-7A1D-4933-9021-2CB0CC7B53AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{E71C7164-E198-422E-8C3D-C5FE1C326B01}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{E71C7164-E198-422E-8C3D-C5FE1C326B01}"/>
   </bookViews>
   <sheets>
     <sheet name="lantai3" sheetId="1" r:id="rId1"/>
@@ -254,8 +254,8 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="MASTER SO"/>
+      <sheetName val="SO Warung"/>
       <sheetName val="Penjualan"/>
-      <sheetName val="SO Warung"/>
       <sheetName val="Sheet2"/>
       <sheetName val="Sheet1"/>
       <sheetName val="Stock Karyawan"/>
@@ -263,8 +263,7 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2">
+      <sheetData sheetId="1">
         <row r="1">
           <cell r="A1" t="str">
             <v>Tanggal</v>
@@ -4784,7 +4783,7 @@
             <v>3</v>
           </cell>
           <cell r="I323">
-            <v>0</v>
+            <v>4</v>
           </cell>
         </row>
         <row r="324">
@@ -4798,7 +4797,7 @@
             <v>3</v>
           </cell>
           <cell r="I324">
-            <v>0</v>
+            <v>6</v>
           </cell>
         </row>
         <row r="325">
@@ -4812,7 +4811,7 @@
             <v>3</v>
           </cell>
           <cell r="I325">
-            <v>0</v>
+            <v>-1</v>
           </cell>
         </row>
         <row r="326">
@@ -4826,7 +4825,7 @@
             <v>3</v>
           </cell>
           <cell r="I326">
-            <v>0</v>
+            <v>-2</v>
           </cell>
         </row>
         <row r="327">
@@ -4840,7 +4839,7 @@
             <v>3</v>
           </cell>
           <cell r="I327">
-            <v>0</v>
+            <v>3</v>
           </cell>
         </row>
         <row r="328">
@@ -4868,7 +4867,7 @@
             <v>3</v>
           </cell>
           <cell r="I329">
-            <v>0</v>
+            <v>-2</v>
           </cell>
         </row>
         <row r="330">
@@ -4882,7 +4881,7 @@
             <v>3</v>
           </cell>
           <cell r="I330">
-            <v>0</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="331">
@@ -4896,7 +4895,7 @@
             <v>3</v>
           </cell>
           <cell r="I331">
-            <v>0</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="332">
@@ -4910,7 +4909,7 @@
             <v>3</v>
           </cell>
           <cell r="I332">
-            <v>0</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="333">
@@ -4938,7 +4937,7 @@
             <v>3</v>
           </cell>
           <cell r="I334">
-            <v>0</v>
+            <v>10</v>
           </cell>
         </row>
         <row r="335">
@@ -4952,7 +4951,7 @@
             <v>3</v>
           </cell>
           <cell r="I335">
-            <v>0</v>
+            <v>4</v>
           </cell>
         </row>
         <row r="336">
@@ -4966,7 +4965,7 @@
             <v>3</v>
           </cell>
           <cell r="I336">
-            <v>0</v>
+            <v>3</v>
           </cell>
         </row>
         <row r="337">
@@ -4994,7 +4993,7 @@
             <v>3</v>
           </cell>
           <cell r="I338">
-            <v>0</v>
+            <v>-3</v>
           </cell>
         </row>
         <row r="339">
@@ -5022,7 +5021,7 @@
             <v>3</v>
           </cell>
           <cell r="I340">
-            <v>0</v>
+            <v>-1</v>
           </cell>
         </row>
         <row r="341">
@@ -5036,7 +5035,7 @@
             <v>3</v>
           </cell>
           <cell r="I341">
-            <v>0</v>
+            <v>13</v>
           </cell>
         </row>
         <row r="342">
@@ -5064,7 +5063,7 @@
             <v>3</v>
           </cell>
           <cell r="I343">
-            <v>0</v>
+            <v>-1</v>
           </cell>
         </row>
         <row r="344">
@@ -5092,7 +5091,7 @@
             <v>8</v>
           </cell>
           <cell r="I345">
-            <v>0</v>
+            <v>5</v>
           </cell>
         </row>
         <row r="346">
@@ -5134,7 +5133,7 @@
             <v>8</v>
           </cell>
           <cell r="I348">
-            <v>0</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="349">
@@ -5148,7 +5147,7 @@
             <v>8</v>
           </cell>
           <cell r="I349">
-            <v>0</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="350">
@@ -5176,7 +5175,7 @@
             <v>8</v>
           </cell>
           <cell r="I351">
-            <v>0</v>
+            <v>3</v>
           </cell>
         </row>
         <row r="352">
@@ -5204,7 +5203,7 @@
             <v>8</v>
           </cell>
           <cell r="I353">
-            <v>0</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="354">
@@ -5218,7 +5217,7 @@
             <v>8</v>
           </cell>
           <cell r="I354">
-            <v>0</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="355">
@@ -5232,7 +5231,7 @@
             <v>8</v>
           </cell>
           <cell r="I355">
-            <v>0</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="356">
@@ -5246,7 +5245,7 @@
             <v>8</v>
           </cell>
           <cell r="I356">
-            <v>0</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="357">
@@ -5260,7 +5259,7 @@
             <v>8</v>
           </cell>
           <cell r="I357">
-            <v>0</v>
+            <v>4</v>
           </cell>
         </row>
         <row r="358">
@@ -5274,7 +5273,7 @@
             <v>8</v>
           </cell>
           <cell r="I358">
-            <v>0</v>
+            <v>3</v>
           </cell>
         </row>
         <row r="359">
@@ -5302,7 +5301,7 @@
             <v>8</v>
           </cell>
           <cell r="I360">
-            <v>0</v>
+            <v>3</v>
           </cell>
         </row>
         <row r="361">
@@ -5316,7 +5315,7 @@
             <v>8</v>
           </cell>
           <cell r="I361">
-            <v>0</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="362">
@@ -5330,7 +5329,7 @@
             <v>8</v>
           </cell>
           <cell r="I362">
-            <v>0</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="363">
@@ -5344,7 +5343,7 @@
             <v>8</v>
           </cell>
           <cell r="I363">
-            <v>0</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="364">
@@ -5358,7 +5357,7 @@
             <v>8</v>
           </cell>
           <cell r="I364">
-            <v>0</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="365">
@@ -5372,7 +5371,7 @@
             <v>9</v>
           </cell>
           <cell r="I365">
-            <v>0</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="366">
@@ -5386,7 +5385,7 @@
             <v>9</v>
           </cell>
           <cell r="I366">
-            <v>0</v>
+            <v>5</v>
           </cell>
         </row>
         <row r="367">
@@ -5428,7 +5427,7 @@
             <v>9</v>
           </cell>
           <cell r="I369">
-            <v>0</v>
+            <v>7</v>
           </cell>
         </row>
         <row r="370">
@@ -5470,7 +5469,7 @@
             <v>9</v>
           </cell>
           <cell r="I372">
-            <v>0</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="373">
@@ -5512,7 +5511,7 @@
             <v>9</v>
           </cell>
           <cell r="I375">
-            <v>0</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="376">
@@ -5526,7 +5525,7 @@
             <v>9</v>
           </cell>
           <cell r="I376">
-            <v>0</v>
+            <v>7</v>
           </cell>
         </row>
         <row r="377">
@@ -5540,7 +5539,7 @@
             <v>9</v>
           </cell>
           <cell r="I377">
-            <v>0</v>
+            <v>3</v>
           </cell>
         </row>
         <row r="378">
@@ -5568,7 +5567,7 @@
             <v>9</v>
           </cell>
           <cell r="I379">
-            <v>0</v>
+            <v>9</v>
           </cell>
         </row>
         <row r="380">
@@ -5596,7 +5595,7 @@
             <v>9</v>
           </cell>
           <cell r="I381">
-            <v>0</v>
+            <v>3</v>
           </cell>
         </row>
         <row r="382">
@@ -5610,7 +5609,7 @@
             <v>9</v>
           </cell>
           <cell r="I382">
-            <v>0</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="383">
@@ -5624,7 +5623,7 @@
             <v>9</v>
           </cell>
           <cell r="I383">
-            <v>0</v>
+            <v>4</v>
           </cell>
         </row>
         <row r="384">
@@ -5638,7 +5637,7 @@
             <v>9</v>
           </cell>
           <cell r="I384">
-            <v>0</v>
+            <v>3</v>
           </cell>
         </row>
         <row r="385">
@@ -5652,892 +5651,11 @@
             <v>9</v>
           </cell>
           <cell r="I385">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="386">
-          <cell r="A386">
-            <v>46155</v>
-          </cell>
-          <cell r="B386" t="str">
-            <v>Bawang Goreng</v>
-          </cell>
-          <cell r="D386">
-            <v>3</v>
-          </cell>
-          <cell r="I386">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="387">
-          <cell r="A387">
-            <v>46155</v>
-          </cell>
-          <cell r="B387" t="str">
-            <v>Keripik Tempe</v>
-          </cell>
-          <cell r="D387">
-            <v>3</v>
-          </cell>
-          <cell r="I387">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="388">
-          <cell r="A388">
-            <v>46155</v>
-          </cell>
-          <cell r="B388" t="str">
-            <v>Keripik Singkong</v>
-          </cell>
-          <cell r="D388">
-            <v>3</v>
-          </cell>
-          <cell r="I388">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="389">
-          <cell r="A389">
-            <v>46155</v>
-          </cell>
-          <cell r="B389" t="str">
-            <v>Kentang Mustofa Daun Jeruk</v>
-          </cell>
-          <cell r="D389">
-            <v>3</v>
-          </cell>
-          <cell r="I389">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="390">
-          <cell r="A390">
-            <v>46155</v>
-          </cell>
-          <cell r="B390" t="str">
-            <v>Komicin</v>
-          </cell>
-          <cell r="D390">
-            <v>3</v>
-          </cell>
-          <cell r="I390">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="391">
-          <cell r="A391">
-            <v>46155</v>
-          </cell>
-          <cell r="B391" t="str">
-            <v>DeSnack</v>
-          </cell>
-          <cell r="D391">
-            <v>3</v>
-          </cell>
-          <cell r="I391">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="392">
-          <cell r="A392">
-            <v>46155</v>
-          </cell>
-          <cell r="B392" t="str">
-            <v>JajanYuk 18</v>
-          </cell>
-          <cell r="D392">
-            <v>3</v>
-          </cell>
-          <cell r="I392">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="393">
-          <cell r="A393">
-            <v>46155</v>
-          </cell>
-          <cell r="B393" t="str">
-            <v>JajanYuk 21</v>
-          </cell>
-          <cell r="D393">
-            <v>3</v>
-          </cell>
-          <cell r="I393">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="394">
-          <cell r="A394">
-            <v>46155</v>
-          </cell>
-          <cell r="B394" t="str">
-            <v>Popcorn ori</v>
-          </cell>
-          <cell r="D394">
-            <v>3</v>
-          </cell>
-          <cell r="I394">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="395">
-          <cell r="A395">
-            <v>46155</v>
-          </cell>
-          <cell r="B395" t="str">
-            <v>Popcorn Rasa</v>
-          </cell>
-          <cell r="D395">
-            <v>3</v>
-          </cell>
-          <cell r="I395">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="396">
-          <cell r="A396">
-            <v>46155</v>
-          </cell>
-          <cell r="B396" t="str">
-            <v>Pop Mie Mini</v>
-          </cell>
-          <cell r="D396">
-            <v>3</v>
-          </cell>
-          <cell r="I396">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="397">
-          <cell r="A397">
-            <v>46155</v>
-          </cell>
-          <cell r="B397" t="str">
-            <v>Mie Gemez</v>
-          </cell>
-          <cell r="D397">
-            <v>3</v>
-          </cell>
-          <cell r="I397">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="398">
-          <cell r="A398">
-            <v>46155</v>
-          </cell>
-          <cell r="B398" t="str">
-            <v>Cheetos</v>
-          </cell>
-          <cell r="D398">
-            <v>3</v>
-          </cell>
-          <cell r="I398">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="399">
-          <cell r="A399">
-            <v>46155</v>
-          </cell>
-          <cell r="B399" t="str">
-            <v>Amplang</v>
-          </cell>
-          <cell r="D399">
-            <v>3</v>
-          </cell>
-          <cell r="I399">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="400">
-          <cell r="A400">
-            <v>46155</v>
-          </cell>
-          <cell r="B400" t="str">
-            <v>Pisang Sale</v>
-          </cell>
-          <cell r="D400">
-            <v>3</v>
-          </cell>
-          <cell r="I400">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="401">
-          <cell r="A401">
-            <v>46155</v>
-          </cell>
-          <cell r="B401" t="str">
-            <v>Kacang Disco</v>
-          </cell>
-          <cell r="D401">
-            <v>3</v>
-          </cell>
-          <cell r="I401">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="402">
-          <cell r="A402">
-            <v>46155</v>
-          </cell>
-          <cell r="B402" t="str">
-            <v>Sari gandum</v>
-          </cell>
-          <cell r="D402">
-            <v>3</v>
-          </cell>
-          <cell r="I402">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="403">
-          <cell r="A403">
-            <v>46155</v>
-          </cell>
-          <cell r="B403" t="str">
-            <v>Yogurt</v>
-          </cell>
-          <cell r="D403">
-            <v>3</v>
-          </cell>
-          <cell r="I403">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="404">
-          <cell r="A404">
-            <v>46155</v>
-          </cell>
-          <cell r="B404" t="str">
-            <v>Lemonilo chimi</v>
-          </cell>
-          <cell r="D404">
-            <v>3</v>
-          </cell>
-          <cell r="I404">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="405">
-          <cell r="A405">
-            <v>46155</v>
-          </cell>
-          <cell r="B405" t="str">
-            <v>PopMie besar</v>
-          </cell>
-          <cell r="D405">
-            <v>3</v>
-          </cell>
-          <cell r="I405">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="406">
-          <cell r="A406">
-            <v>46155</v>
-          </cell>
-          <cell r="B406" t="str">
-            <v>YouC</v>
-          </cell>
-          <cell r="D406">
-            <v>3</v>
-          </cell>
-          <cell r="I406">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="407">
-          <cell r="A407">
-            <v>46155</v>
-          </cell>
-          <cell r="B407" t="str">
-            <v>Bawang Goreng</v>
-          </cell>
-          <cell r="D407">
-            <v>8</v>
-          </cell>
-          <cell r="I407">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="408">
-          <cell r="A408">
-            <v>46155</v>
-          </cell>
-          <cell r="B408" t="str">
-            <v>Keripik Tempe</v>
-          </cell>
-          <cell r="D408">
-            <v>8</v>
-          </cell>
-          <cell r="I408">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="409">
-          <cell r="A409">
-            <v>46155</v>
-          </cell>
-          <cell r="B409" t="str">
-            <v>Keripik Singkong</v>
-          </cell>
-          <cell r="D409">
-            <v>8</v>
-          </cell>
-          <cell r="I409">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="410">
-          <cell r="A410">
-            <v>46155</v>
-          </cell>
-          <cell r="B410" t="str">
-            <v>Kentang Mustofa Daun Jeruk</v>
-          </cell>
-          <cell r="D410">
-            <v>8</v>
-          </cell>
-          <cell r="I410">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="411">
-          <cell r="A411">
-            <v>46155</v>
-          </cell>
-          <cell r="B411" t="str">
-            <v>Komicin</v>
-          </cell>
-          <cell r="D411">
-            <v>8</v>
-          </cell>
-          <cell r="I411">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="412">
-          <cell r="A412">
-            <v>46155</v>
-          </cell>
-          <cell r="B412" t="str">
-            <v>DeSnack</v>
-          </cell>
-          <cell r="D412">
-            <v>8</v>
-          </cell>
-          <cell r="I412">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="413">
-          <cell r="A413">
-            <v>46155</v>
-          </cell>
-          <cell r="B413" t="str">
-            <v>JajanYuk 18</v>
-          </cell>
-          <cell r="D413">
-            <v>8</v>
-          </cell>
-          <cell r="I413">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="414">
-          <cell r="A414">
-            <v>46155</v>
-          </cell>
-          <cell r="B414" t="str">
-            <v>JajanYuk 21</v>
-          </cell>
-          <cell r="D414">
-            <v>8</v>
-          </cell>
-          <cell r="I414">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="415">
-          <cell r="A415">
-            <v>46155</v>
-          </cell>
-          <cell r="B415" t="str">
-            <v>Popcorn ori</v>
-          </cell>
-          <cell r="D415">
-            <v>8</v>
-          </cell>
-          <cell r="I415">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="416">
-          <cell r="A416">
-            <v>46155</v>
-          </cell>
-          <cell r="B416" t="str">
-            <v>Popcorn Rasa</v>
-          </cell>
-          <cell r="D416">
-            <v>8</v>
-          </cell>
-          <cell r="I416">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="417">
-          <cell r="A417">
-            <v>46155</v>
-          </cell>
-          <cell r="B417" t="str">
-            <v>Pop Mie Mini</v>
-          </cell>
-          <cell r="D417">
-            <v>8</v>
-          </cell>
-          <cell r="I417">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="418">
-          <cell r="A418">
-            <v>46155</v>
-          </cell>
-          <cell r="B418" t="str">
-            <v>Mie Gemez</v>
-          </cell>
-          <cell r="D418">
-            <v>8</v>
-          </cell>
-          <cell r="I418">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="419">
-          <cell r="A419">
-            <v>46155</v>
-          </cell>
-          <cell r="B419" t="str">
-            <v>Cheetos</v>
-          </cell>
-          <cell r="D419">
-            <v>8</v>
-          </cell>
-          <cell r="I419">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="420">
-          <cell r="A420">
-            <v>46155</v>
-          </cell>
-          <cell r="B420" t="str">
-            <v>Amplang</v>
-          </cell>
-          <cell r="D420">
-            <v>8</v>
-          </cell>
-          <cell r="I420">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="421">
-          <cell r="A421">
-            <v>46155</v>
-          </cell>
-          <cell r="B421" t="str">
-            <v>Pisang Sale</v>
-          </cell>
-          <cell r="D421">
-            <v>8</v>
-          </cell>
-          <cell r="I421">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="422">
-          <cell r="A422">
-            <v>46155</v>
-          </cell>
-          <cell r="B422" t="str">
-            <v>Kacang Disco</v>
-          </cell>
-          <cell r="D422">
-            <v>8</v>
-          </cell>
-          <cell r="I422">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="423">
-          <cell r="A423">
-            <v>46155</v>
-          </cell>
-          <cell r="B423" t="str">
-            <v>Sari gandum</v>
-          </cell>
-          <cell r="D423">
-            <v>8</v>
-          </cell>
-          <cell r="I423">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="424">
-          <cell r="A424">
-            <v>46155</v>
-          </cell>
-          <cell r="B424" t="str">
-            <v>Yogurt</v>
-          </cell>
-          <cell r="D424">
-            <v>8</v>
-          </cell>
-          <cell r="I424">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="425">
-          <cell r="A425">
-            <v>46155</v>
-          </cell>
-          <cell r="B425" t="str">
-            <v>Lemonilo chimi</v>
-          </cell>
-          <cell r="D425">
-            <v>8</v>
-          </cell>
-          <cell r="I425">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="426">
-          <cell r="A426">
-            <v>46155</v>
-          </cell>
-          <cell r="B426" t="str">
-            <v>PopMie besar</v>
-          </cell>
-          <cell r="D426">
-            <v>8</v>
-          </cell>
-          <cell r="I426">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="427">
-          <cell r="A427">
-            <v>46155</v>
-          </cell>
-          <cell r="B427" t="str">
-            <v>YouC</v>
-          </cell>
-          <cell r="D427">
-            <v>8</v>
-          </cell>
-          <cell r="I427">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="428">
-          <cell r="A428">
-            <v>46155</v>
-          </cell>
-          <cell r="B428" t="str">
-            <v>Bawang Goreng</v>
-          </cell>
-          <cell r="D428">
-            <v>9</v>
-          </cell>
-          <cell r="I428">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="429">
-          <cell r="A429">
-            <v>46155</v>
-          </cell>
-          <cell r="B429" t="str">
-            <v>Keripik Tempe</v>
-          </cell>
-          <cell r="D429">
-            <v>9</v>
-          </cell>
-          <cell r="I429">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="430">
-          <cell r="A430">
-            <v>46155</v>
-          </cell>
-          <cell r="B430" t="str">
-            <v>Keripik Singkong</v>
-          </cell>
-          <cell r="D430">
-            <v>9</v>
-          </cell>
-          <cell r="I430">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="431">
-          <cell r="A431">
-            <v>46155</v>
-          </cell>
-          <cell r="B431" t="str">
-            <v>Kentang Mustofa Daun Jeruk</v>
-          </cell>
-          <cell r="D431">
-            <v>9</v>
-          </cell>
-          <cell r="I431">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="432">
-          <cell r="A432">
-            <v>46155</v>
-          </cell>
-          <cell r="B432" t="str">
-            <v>Komicin</v>
-          </cell>
-          <cell r="D432">
-            <v>9</v>
-          </cell>
-          <cell r="I432">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="433">
-          <cell r="A433">
-            <v>46155</v>
-          </cell>
-          <cell r="B433" t="str">
-            <v>DeSnack</v>
-          </cell>
-          <cell r="D433">
-            <v>9</v>
-          </cell>
-          <cell r="I433">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="434">
-          <cell r="A434">
-            <v>46155</v>
-          </cell>
-          <cell r="B434" t="str">
-            <v>JajanYuk 18</v>
-          </cell>
-          <cell r="D434">
-            <v>9</v>
-          </cell>
-          <cell r="I434">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="435">
-          <cell r="A435">
-            <v>46155</v>
-          </cell>
-          <cell r="B435" t="str">
-            <v>JajanYuk 21</v>
-          </cell>
-          <cell r="D435">
-            <v>9</v>
-          </cell>
-          <cell r="I435">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="436">
-          <cell r="A436">
-            <v>46155</v>
-          </cell>
-          <cell r="B436" t="str">
-            <v>Popcorn ori</v>
-          </cell>
-          <cell r="D436">
-            <v>9</v>
-          </cell>
-          <cell r="I436">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="437">
-          <cell r="A437">
-            <v>46155</v>
-          </cell>
-          <cell r="B437" t="str">
-            <v>Popcorn Rasa</v>
-          </cell>
-          <cell r="D437">
-            <v>9</v>
-          </cell>
-          <cell r="I437">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="438">
-          <cell r="A438">
-            <v>46155</v>
-          </cell>
-          <cell r="B438" t="str">
-            <v>Pop Mie Mini</v>
-          </cell>
-          <cell r="D438">
-            <v>9</v>
-          </cell>
-          <cell r="I438">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="439">
-          <cell r="A439">
-            <v>46155</v>
-          </cell>
-          <cell r="B439" t="str">
-            <v>Mie Gemez</v>
-          </cell>
-          <cell r="D439">
-            <v>9</v>
-          </cell>
-          <cell r="I439">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="440">
-          <cell r="A440">
-            <v>46155</v>
-          </cell>
-          <cell r="B440" t="str">
-            <v>Cheetos</v>
-          </cell>
-          <cell r="D440">
-            <v>9</v>
-          </cell>
-          <cell r="I440">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="441">
-          <cell r="A441">
-            <v>46155</v>
-          </cell>
-          <cell r="B441" t="str">
-            <v>Amplang</v>
-          </cell>
-          <cell r="D441">
-            <v>9</v>
-          </cell>
-          <cell r="I441">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="442">
-          <cell r="A442">
-            <v>46155</v>
-          </cell>
-          <cell r="B442" t="str">
-            <v>Pisang Sale</v>
-          </cell>
-          <cell r="D442">
-            <v>9</v>
-          </cell>
-          <cell r="I442">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="443">
-          <cell r="A443">
-            <v>46155</v>
-          </cell>
-          <cell r="B443" t="str">
-            <v>Kacang Disco</v>
-          </cell>
-          <cell r="D443">
-            <v>9</v>
-          </cell>
-          <cell r="I443">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="444">
-          <cell r="A444">
-            <v>46155</v>
-          </cell>
-          <cell r="B444" t="str">
-            <v>Sari gandum</v>
-          </cell>
-          <cell r="D444">
-            <v>9</v>
-          </cell>
-          <cell r="I444">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="445">
-          <cell r="A445">
-            <v>46155</v>
-          </cell>
-          <cell r="B445" t="str">
-            <v>Yogurt</v>
-          </cell>
-          <cell r="D445">
-            <v>9</v>
-          </cell>
-          <cell r="I445">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="446">
-          <cell r="A446">
-            <v>46155</v>
-          </cell>
-          <cell r="B446" t="str">
-            <v>Lemonilo chimi</v>
-          </cell>
-          <cell r="D446">
-            <v>9</v>
-          </cell>
-          <cell r="I446">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="447">
-          <cell r="A447">
-            <v>46155</v>
-          </cell>
-          <cell r="B447" t="str">
-            <v>PopMie besar</v>
-          </cell>
-          <cell r="D447">
-            <v>9</v>
-          </cell>
-          <cell r="I447">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="448">
-          <cell r="A448">
-            <v>46155</v>
-          </cell>
-          <cell r="B448" t="str">
-            <v>YouC</v>
-          </cell>
-          <cell r="D448">
-            <v>9</v>
-          </cell>
-          <cell r="I448">
-            <v>4</v>
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="2"/>
       <sheetData sheetId="3"/>
       <sheetData sheetId="4"/>
       <sheetData sheetId="5"/>
@@ -6908,11 +6026,11 @@
       </c>
       <c r="E2" s="4">
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A2,'[1]SO Warung'!$B:$B,B2,'[1]SO Warung'!$D:$D,C2)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F2" s="4">
         <f>D2-E2</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G2" s="6">
         <v>35000</v>
@@ -6934,11 +6052,11 @@
       </c>
       <c r="E3" s="4">
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A3,'[1]SO Warung'!$B:$B,B3,'[1]SO Warung'!$D:$D,C3)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F3" s="4">
         <f t="shared" ref="F3:F24" si="0">D3-E3</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G3" s="6">
         <v>23000</v>
@@ -6960,11 +6078,11 @@
       </c>
       <c r="E4" s="4">
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A4,'[1]SO Warung'!$B:$B,B4,'[1]SO Warung'!$D:$D,C4)</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F4" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4" s="6">
         <v>21000</v>
@@ -6986,11 +6104,11 @@
       </c>
       <c r="E5" s="4">
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A5,'[1]SO Warung'!$B:$B,B5,'[1]SO Warung'!$D:$D,C5)</f>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="F5" s="4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G5" s="6">
         <v>36000</v>
@@ -7012,11 +6130,11 @@
       </c>
       <c r="E6" s="4">
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A6,'[1]SO Warung'!$B:$B,B6,'[1]SO Warung'!$D:$D,C6)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F6" s="4">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G6" s="6">
         <v>23000</v>
@@ -7116,11 +6234,11 @@
       </c>
       <c r="E10" s="4">
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A10,'[1]SO Warung'!$B:$B,B10,'[1]SO Warung'!$D:$D,C10)</f>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="F10" s="4">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G10" s="6">
         <v>18000</v>
@@ -7142,11 +6260,11 @@
       </c>
       <c r="E11" s="4">
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A11,'[1]SO Warung'!$B:$B,B11,'[1]SO Warung'!$D:$D,C11)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G11" s="6">
         <v>21000</v>
@@ -7168,11 +6286,11 @@
       </c>
       <c r="E12" s="4">
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A12,'[1]SO Warung'!$B:$B,B12,'[1]SO Warung'!$D:$D,C12)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G12" s="6">
         <v>35000</v>
@@ -7194,11 +6312,11 @@
       </c>
       <c r="E13" s="4">
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A13,'[1]SO Warung'!$B:$B,B13,'[1]SO Warung'!$D:$D,C13)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F13" s="4">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G13" s="6">
         <v>40000</v>
@@ -7246,11 +6364,11 @@
       </c>
       <c r="E15" s="4">
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A15,'[1]SO Warung'!$B:$B,B15,'[1]SO Warung'!$D:$D,C15)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F15" s="4">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G15" s="6">
         <v>2000</v>
@@ -7272,11 +6390,11 @@
       </c>
       <c r="E16" s="4">
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A16,'[1]SO Warung'!$B:$B,B16,'[1]SO Warung'!$D:$D,C16)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F16" s="4">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G16" s="6">
         <v>2500</v>
@@ -7298,11 +6416,11 @@
       </c>
       <c r="E17" s="4">
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A17,'[1]SO Warung'!$B:$B,B17,'[1]SO Warung'!$D:$D,C17)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F17" s="4">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G17" s="6">
         <v>10000</v>
@@ -7350,11 +6468,11 @@
       </c>
       <c r="E19" s="4">
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A19,'[1]SO Warung'!$B:$B,B19,'[1]SO Warung'!$D:$D,C19)</f>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="F19" s="4">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G19" s="6">
         <v>23000</v>
@@ -7402,11 +6520,11 @@
       </c>
       <c r="E21" s="4">
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A21,'[1]SO Warung'!$B:$B,B21,'[1]SO Warung'!$D:$D,C21)</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F21" s="4">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G21" s="6">
         <v>14500</v>
@@ -7428,11 +6546,11 @@
       </c>
       <c r="E22" s="4">
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A22,'[1]SO Warung'!$B:$B,B22,'[1]SO Warung'!$D:$D,C22)</f>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F22" s="4">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="G22" s="6">
         <v>3500</v>
@@ -7480,11 +6598,11 @@
       </c>
       <c r="E24" s="4">
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A24,'[1]SO Warung'!$B:$B,B24,'[1]SO Warung'!$D:$D,C24)</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F24" s="4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G24" s="6">
         <v>9000</v>
@@ -7561,7 +6679,7 @@
       </c>
       <c r="E3" s="5">
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A3,'[1]SO Warung'!$B:$B,B3,'[1]SO Warung'!$D:$D,C3)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F3" s="6">
         <v>23000</v>
@@ -7627,7 +6745,7 @@
       </c>
       <c r="E6" s="5">
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A6,'[1]SO Warung'!$B:$B,B6,'[1]SO Warung'!$D:$D,C6)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="6">
         <v>23000</v>
@@ -7649,7 +6767,7 @@
       </c>
       <c r="E7" s="5">
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A7,'[1]SO Warung'!$B:$B,B7,'[1]SO Warung'!$D:$D,C7)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="6">
         <v>15000</v>
@@ -7737,7 +6855,7 @@
       </c>
       <c r="E11" s="5">
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A11,'[1]SO Warung'!$B:$B,B11,'[1]SO Warung'!$D:$D,C11)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F11" s="6">
         <v>21000</v>
@@ -7781,7 +6899,7 @@
       </c>
       <c r="E13" s="5">
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A13,'[1]SO Warung'!$B:$B,B13,'[1]SO Warung'!$D:$D,C13)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F13" s="6">
         <v>40000</v>
@@ -7803,7 +6921,7 @@
       </c>
       <c r="E14" s="5">
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A14,'[1]SO Warung'!$B:$B,B14,'[1]SO Warung'!$D:$D,C14)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="6">
         <v>2500</v>
@@ -7825,7 +6943,7 @@
       </c>
       <c r="E15" s="5">
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A15,'[1]SO Warung'!$B:$B,B15,'[1]SO Warung'!$D:$D,C15)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="6">
         <v>2000</v>
@@ -7847,7 +6965,7 @@
       </c>
       <c r="E16" s="5">
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A16,'[1]SO Warung'!$B:$B,B16,'[1]SO Warung'!$D:$D,C16)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F16" s="6">
         <v>2500</v>
@@ -7869,7 +6987,7 @@
       </c>
       <c r="E17" s="5">
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A17,'[1]SO Warung'!$B:$B,B17,'[1]SO Warung'!$D:$D,C17)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F17" s="6">
         <v>10000</v>
@@ -7891,7 +7009,7 @@
       </c>
       <c r="E18" s="5">
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A18,'[1]SO Warung'!$B:$B,B18,'[1]SO Warung'!$D:$D,C18)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F18" s="6">
         <v>15000</v>
@@ -7935,7 +7053,7 @@
       </c>
       <c r="E20" s="5">
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A20,'[1]SO Warung'!$B:$B,B20,'[1]SO Warung'!$D:$D,C20)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F20" s="6">
         <v>11000</v>
@@ -7957,7 +7075,7 @@
       </c>
       <c r="E21" s="5">
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A21,'[1]SO Warung'!$B:$B,B21,'[1]SO Warung'!$D:$D,C21)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F21" s="6">
         <v>14500</v>
@@ -7979,7 +7097,7 @@
       </c>
       <c r="E22" s="5">
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A22,'[1]SO Warung'!$B:$B,B22,'[1]SO Warung'!$D:$D,C22)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F22" s="6">
         <v>3500</v>
@@ -8001,7 +7119,7 @@
       </c>
       <c r="E23" s="5">
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A23,'[1]SO Warung'!$B:$B,B23,'[1]SO Warung'!$D:$D,C23)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="6">
         <v>5500</v>
@@ -8023,7 +7141,7 @@
       </c>
       <c r="E24" s="5">
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A24,'[1]SO Warung'!$B:$B,B24,'[1]SO Warung'!$D:$D,C24)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F24" s="6">
         <v>9000</v>
@@ -8081,7 +7199,7 @@
       </c>
       <c r="E2" s="5">
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A2,'[1]SO Warung'!$B:$B,B2,'[1]SO Warung'!$D:$D,C2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="6">
         <v>35000</v>
@@ -8103,7 +7221,7 @@
       </c>
       <c r="E3" s="5">
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A3,'[1]SO Warung'!$B:$B,B3,'[1]SO Warung'!$D:$D,C3)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F3" s="6">
         <v>23000</v>
@@ -8169,7 +7287,7 @@
       </c>
       <c r="E6" s="5">
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A6,'[1]SO Warung'!$B:$B,B6,'[1]SO Warung'!$D:$D,C6)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F6" s="6">
         <v>23000</v>
@@ -8279,7 +7397,7 @@
       </c>
       <c r="E11" s="5">
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A11,'[1]SO Warung'!$B:$B,B11,'[1]SO Warung'!$D:$D,C11)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="6">
         <v>21000</v>
@@ -8345,7 +7463,7 @@
       </c>
       <c r="E14" s="5">
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A14,'[1]SO Warung'!$B:$B,B14,'[1]SO Warung'!$D:$D,C14)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F14" s="6">
         <v>2500</v>
@@ -8367,7 +7485,7 @@
       </c>
       <c r="E15" s="5">
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A15,'[1]SO Warung'!$B:$B,B15,'[1]SO Warung'!$D:$D,C15)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F15" s="6">
         <v>2000</v>
@@ -8389,7 +7507,7 @@
       </c>
       <c r="E16" s="5">
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A16,'[1]SO Warung'!$B:$B,B16,'[1]SO Warung'!$D:$D,C16)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F16" s="6">
         <v>2500</v>
@@ -8433,7 +7551,7 @@
       </c>
       <c r="E18" s="5">
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A18,'[1]SO Warung'!$B:$B,B18,'[1]SO Warung'!$D:$D,C18)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F18" s="6">
         <v>15000</v>
@@ -8477,7 +7595,7 @@
       </c>
       <c r="E20" s="5">
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A20,'[1]SO Warung'!$B:$B,B20,'[1]SO Warung'!$D:$D,C20)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F20" s="6">
         <v>11000</v>
@@ -8499,7 +7617,7 @@
       </c>
       <c r="E21" s="5">
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A21,'[1]SO Warung'!$B:$B,B21,'[1]SO Warung'!$D:$D,C21)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" s="6">
         <v>14500</v>
@@ -8521,7 +7639,7 @@
       </c>
       <c r="E22" s="5">
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A22,'[1]SO Warung'!$B:$B,B22,'[1]SO Warung'!$D:$D,C22)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F22" s="6">
         <v>3500</v>
@@ -8543,7 +7661,7 @@
       </c>
       <c r="E23" s="5">
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A23,'[1]SO Warung'!$B:$B,B23,'[1]SO Warung'!$D:$D,C23)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F23" s="6">
         <v>5500</v>
@@ -8565,7 +7683,7 @@
       </c>
       <c r="E24" s="5">
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A24,'[1]SO Warung'!$B:$B,B24,'[1]SO Warung'!$D:$D,C24)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" s="6">
         <v>9000</v>

--- a/data/master_data.xlsx
+++ b/data/master_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\68766\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF5321DA-7A1D-4933-9021-2CB0CC7B53AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F52A79D-CE6E-4B9B-96EF-7B05620F6B1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{E71C7164-E198-422E-8C3D-C5FE1C326B01}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{E71C7164-E198-422E-8C3D-C5FE1C326B01}"/>
   </bookViews>
   <sheets>
     <sheet name="lantai3" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="31">
   <si>
     <t>Tanggal</t>
   </si>
@@ -6616,10 +6616,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FC81ECA-A7E4-405E-8E37-17F94A153613}">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultColWidth="18.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -6636,13 +6636,16 @@
         <v>3</v>
       </c>
       <c r="F1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>46154</v>
       </c>
@@ -6659,12 +6662,16 @@
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A2,'[1]SO Warung'!$B:$B,B2,'[1]SO Warung'!$D:$D,C2)</f>
         <v>0</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="5">
+        <f>D2-E2</f>
+        <v>5</v>
+      </c>
+      <c r="G2" s="6">
         <v>35000</v>
       </c>
-      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
     </row>
-    <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>46154</v>
       </c>
@@ -6681,12 +6688,16 @@
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A3,'[1]SO Warung'!$B:$B,B3,'[1]SO Warung'!$D:$D,C3)</f>
         <v>5</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="5">
+        <f t="shared" ref="F3:F24" si="0">D3-E3</f>
+        <v>1</v>
+      </c>
+      <c r="G3" s="6">
         <v>23000</v>
       </c>
-      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>46154</v>
       </c>
@@ -6703,12 +6714,16 @@
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A4,'[1]SO Warung'!$B:$B,B4,'[1]SO Warung'!$D:$D,C4)</f>
         <v>0</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G4" s="6">
         <v>21000</v>
       </c>
-      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:7" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>46154</v>
       </c>
@@ -6725,12 +6740,16 @@
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A5,'[1]SO Warung'!$B:$B,B5,'[1]SO Warung'!$D:$D,C5)</f>
         <v>0</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="5">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G5" s="6">
         <v>36000</v>
       </c>
-      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>46154</v>
       </c>
@@ -6747,12 +6766,16 @@
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A6,'[1]SO Warung'!$B:$B,B6,'[1]SO Warung'!$D:$D,C6)</f>
         <v>1</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="5">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="6">
         <v>23000</v>
       </c>
-      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>46154</v>
       </c>
@@ -6769,12 +6792,16 @@
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A7,'[1]SO Warung'!$B:$B,B7,'[1]SO Warung'!$D:$D,C7)</f>
         <v>1</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="5">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="G7" s="6">
         <v>15000</v>
       </c>
-      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
     </row>
-    <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>46154</v>
       </c>
@@ -6791,12 +6818,16 @@
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A8,'[1]SO Warung'!$B:$B,B8,'[1]SO Warung'!$D:$D,C8)</f>
         <v>0</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="5">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="G8" s="6">
         <v>18000</v>
       </c>
-      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
     </row>
-    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>46154</v>
       </c>
@@ -6813,12 +6844,16 @@
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A9,'[1]SO Warung'!$B:$B,B9,'[1]SO Warung'!$D:$D,C9)</f>
         <v>0</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G9" s="6">
         <v>21000</v>
       </c>
-      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>46154</v>
       </c>
@@ -6835,12 +6870,16 @@
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A10,'[1]SO Warung'!$B:$B,B10,'[1]SO Warung'!$D:$D,C10)</f>
         <v>0</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="5">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G10" s="6">
         <v>18000</v>
       </c>
-      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
     </row>
-    <row r="11" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>46154</v>
       </c>
@@ -6857,12 +6896,16 @@
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A11,'[1]SO Warung'!$B:$B,B11,'[1]SO Warung'!$D:$D,C11)</f>
         <v>3</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G11" s="6">
         <v>21000</v>
       </c>
-      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
     </row>
-    <row r="12" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>46154</v>
       </c>
@@ -6879,12 +6922,16 @@
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A12,'[1]SO Warung'!$B:$B,B12,'[1]SO Warung'!$D:$D,C12)</f>
         <v>0</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G12" s="6">
         <v>35000</v>
       </c>
-      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
     </row>
-    <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>46154</v>
       </c>
@@ -6901,12 +6948,16 @@
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A13,'[1]SO Warung'!$B:$B,B13,'[1]SO Warung'!$D:$D,C13)</f>
         <v>2</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G13" s="6">
         <v>40000</v>
       </c>
-      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
     </row>
-    <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>46154</v>
       </c>
@@ -6923,12 +6974,16 @@
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A14,'[1]SO Warung'!$B:$B,B14,'[1]SO Warung'!$D:$D,C14)</f>
         <v>1</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="5">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="G14" s="6">
         <v>2500</v>
       </c>
-      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
     </row>
-    <row r="15" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>46154</v>
       </c>
@@ -6945,12 +7000,16 @@
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A15,'[1]SO Warung'!$B:$B,B15,'[1]SO Warung'!$D:$D,C15)</f>
         <v>1</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="5">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="G15" s="6">
         <v>2000</v>
       </c>
-      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
     </row>
-    <row r="16" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>46154</v>
       </c>
@@ -6967,12 +7026,16 @@
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A16,'[1]SO Warung'!$B:$B,B16,'[1]SO Warung'!$D:$D,C16)</f>
         <v>2</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="5">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="G16" s="6">
         <v>2500</v>
       </c>
-      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
     </row>
-    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>46154</v>
       </c>
@@ -6989,12 +7052,16 @@
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A17,'[1]SO Warung'!$B:$B,B17,'[1]SO Warung'!$D:$D,C17)</f>
         <v>4</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F17" s="5">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="G17" s="6">
         <v>10000</v>
       </c>
-      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
     </row>
-    <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>46154</v>
       </c>
@@ -7011,12 +7078,16 @@
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A18,'[1]SO Warung'!$B:$B,B18,'[1]SO Warung'!$D:$D,C18)</f>
         <v>3</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F18" s="5">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="G18" s="6">
         <v>15000</v>
       </c>
-      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
     </row>
-    <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>46154</v>
       </c>
@@ -7033,12 +7104,16 @@
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A19,'[1]SO Warung'!$B:$B,B19,'[1]SO Warung'!$D:$D,C19)</f>
         <v>0</v>
       </c>
-      <c r="F19" s="6">
+      <c r="F19" s="5">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="G19" s="6">
         <v>23000</v>
       </c>
-      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
     </row>
-    <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>46154</v>
       </c>
@@ -7055,12 +7130,16 @@
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A20,'[1]SO Warung'!$B:$B,B20,'[1]SO Warung'!$D:$D,C20)</f>
         <v>3</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F20" s="5">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="G20" s="6">
         <v>11000</v>
       </c>
-      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
     </row>
-    <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>46154</v>
       </c>
@@ -7077,12 +7156,16 @@
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A21,'[1]SO Warung'!$B:$B,B21,'[1]SO Warung'!$D:$D,C21)</f>
         <v>2</v>
       </c>
-      <c r="F21" s="6">
+      <c r="F21" s="5">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G21" s="6">
         <v>14500</v>
       </c>
-      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
     </row>
-    <row r="22" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>46154</v>
       </c>
@@ -7099,12 +7182,16 @@
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A22,'[1]SO Warung'!$B:$B,B22,'[1]SO Warung'!$D:$D,C22)</f>
         <v>2</v>
       </c>
-      <c r="F22" s="6">
+      <c r="F22" s="5">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="G22" s="6">
         <v>3500</v>
       </c>
-      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
     </row>
-    <row r="23" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>46154</v>
       </c>
@@ -7121,12 +7208,16 @@
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A23,'[1]SO Warung'!$B:$B,B23,'[1]SO Warung'!$D:$D,C23)</f>
         <v>1</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F23" s="5">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="G23" s="6">
         <v>5500</v>
       </c>
-      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
     </row>
-    <row r="24" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>46154</v>
       </c>
@@ -7143,10 +7234,14 @@
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A24,'[1]SO Warung'!$B:$B,B24,'[1]SO Warung'!$D:$D,C24)</f>
         <v>2</v>
       </c>
-      <c r="F24" s="6">
+      <c r="F24" s="5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G24" s="6">
         <v>9000</v>
       </c>
-      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7155,13 +7250,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1DCE441-CDA4-4A53-89BE-162F338C8637}">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultColWidth="17.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="26.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -7178,13 +7273,16 @@
         <v>3</v>
       </c>
       <c r="F1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>46154</v>
       </c>
@@ -7201,12 +7299,16 @@
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A2,'[1]SO Warung'!$B:$B,B2,'[1]SO Warung'!$D:$D,C2)</f>
         <v>1</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="5">
+        <f>D2-E2</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="6">
         <v>35000</v>
       </c>
-      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
     </row>
-    <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>46154</v>
       </c>
@@ -7223,12 +7325,16 @@
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A3,'[1]SO Warung'!$B:$B,B3,'[1]SO Warung'!$D:$D,C3)</f>
         <v>5</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="5">
+        <f t="shared" ref="F3:F24" si="0">D3-E3</f>
+        <v>1</v>
+      </c>
+      <c r="G3" s="6">
         <v>23000</v>
       </c>
-      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>46154</v>
       </c>
@@ -7245,12 +7351,16 @@
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A4,'[1]SO Warung'!$B:$B,B4,'[1]SO Warung'!$D:$D,C4)</f>
         <v>0</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G4" s="6">
         <v>21000</v>
       </c>
-      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:7" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>46154</v>
       </c>
@@ -7267,12 +7377,16 @@
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A5,'[1]SO Warung'!$B:$B,B5,'[1]SO Warung'!$D:$D,C5)</f>
         <v>0</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="5">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G5" s="6">
         <v>36000</v>
       </c>
-      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>46154</v>
       </c>
@@ -7289,12 +7403,16 @@
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A6,'[1]SO Warung'!$B:$B,B6,'[1]SO Warung'!$D:$D,C6)</f>
         <v>7</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="5">
+        <f t="shared" si="0"/>
+        <v>-2</v>
+      </c>
+      <c r="G6" s="6">
         <v>23000</v>
       </c>
-      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>46154</v>
       </c>
@@ -7311,12 +7429,16 @@
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A7,'[1]SO Warung'!$B:$B,B7,'[1]SO Warung'!$D:$D,C7)</f>
         <v>0</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="5">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="G7" s="6">
         <v>15000</v>
       </c>
-      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
     </row>
-    <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>46154</v>
       </c>
@@ -7333,12 +7455,16 @@
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A8,'[1]SO Warung'!$B:$B,B8,'[1]SO Warung'!$D:$D,C8)</f>
         <v>0</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="5">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="G8" s="6">
         <v>18000</v>
       </c>
-      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
     </row>
-    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>46154</v>
       </c>
@@ -7355,12 +7481,16 @@
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A9,'[1]SO Warung'!$B:$B,B9,'[1]SO Warung'!$D:$D,C9)</f>
         <v>0</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G9" s="6">
         <v>21000</v>
       </c>
-      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>46154</v>
       </c>
@@ -7377,12 +7507,16 @@
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A10,'[1]SO Warung'!$B:$B,B10,'[1]SO Warung'!$D:$D,C10)</f>
         <v>0</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="5">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G10" s="6">
         <v>18000</v>
       </c>
-      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
     </row>
-    <row r="11" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>46154</v>
       </c>
@@ -7399,12 +7533,16 @@
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A11,'[1]SO Warung'!$B:$B,B11,'[1]SO Warung'!$D:$D,C11)</f>
         <v>1</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G11" s="6">
         <v>21000</v>
       </c>
-      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
     </row>
-    <row r="12" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>46154</v>
       </c>
@@ -7421,12 +7559,16 @@
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A12,'[1]SO Warung'!$B:$B,B12,'[1]SO Warung'!$D:$D,C12)</f>
         <v>0</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G12" s="6">
         <v>35000</v>
       </c>
-      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
     </row>
-    <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>46154</v>
       </c>
@@ -7443,12 +7585,16 @@
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A13,'[1]SO Warung'!$B:$B,B13,'[1]SO Warung'!$D:$D,C13)</f>
         <v>0</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="5">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G13" s="6">
         <v>40000</v>
       </c>
-      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
     </row>
-    <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>46154</v>
       </c>
@@ -7465,12 +7611,16 @@
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A14,'[1]SO Warung'!$B:$B,B14,'[1]SO Warung'!$D:$D,C14)</f>
         <v>2</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="5">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="G14" s="6">
         <v>2500</v>
       </c>
-      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
     </row>
-    <row r="15" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>46154</v>
       </c>
@@ -7487,12 +7637,16 @@
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A15,'[1]SO Warung'!$B:$B,B15,'[1]SO Warung'!$D:$D,C15)</f>
         <v>7</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="5">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G15" s="6">
         <v>2000</v>
       </c>
-      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
     </row>
-    <row r="16" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>46154</v>
       </c>
@@ -7509,12 +7663,16 @@
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A16,'[1]SO Warung'!$B:$B,B16,'[1]SO Warung'!$D:$D,C16)</f>
         <v>3</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="5">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="G16" s="6">
         <v>2500</v>
       </c>
-      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
     </row>
-    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>46154</v>
       </c>
@@ -7531,12 +7689,16 @@
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A17,'[1]SO Warung'!$B:$B,B17,'[1]SO Warung'!$D:$D,C17)</f>
         <v>0</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F17" s="5">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="G17" s="6">
         <v>10000</v>
       </c>
-      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
     </row>
-    <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>46154</v>
       </c>
@@ -7553,12 +7715,16 @@
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A18,'[1]SO Warung'!$B:$B,B18,'[1]SO Warung'!$D:$D,C18)</f>
         <v>9</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F18" s="5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G18" s="6">
         <v>15000</v>
       </c>
-      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
     </row>
-    <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>46154</v>
       </c>
@@ -7575,12 +7741,16 @@
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A19,'[1]SO Warung'!$B:$B,B19,'[1]SO Warung'!$D:$D,C19)</f>
         <v>0</v>
       </c>
-      <c r="F19" s="6">
+      <c r="F19" s="5">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="G19" s="6">
         <v>23000</v>
       </c>
-      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
     </row>
-    <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>46154</v>
       </c>
@@ -7597,12 +7767,16 @@
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A20,'[1]SO Warung'!$B:$B,B20,'[1]SO Warung'!$D:$D,C20)</f>
         <v>3</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F20" s="5">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="G20" s="6">
         <v>11000</v>
       </c>
-      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
     </row>
-    <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>46154</v>
       </c>
@@ -7619,12 +7793,16 @@
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A21,'[1]SO Warung'!$B:$B,B21,'[1]SO Warung'!$D:$D,C21)</f>
         <v>1</v>
       </c>
-      <c r="F21" s="6">
+      <c r="F21" s="5">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="G21" s="6">
         <v>14500</v>
       </c>
-      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
     </row>
-    <row r="22" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>46154</v>
       </c>
@@ -7641,12 +7819,16 @@
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A22,'[1]SO Warung'!$B:$B,B22,'[1]SO Warung'!$D:$D,C22)</f>
         <v>4</v>
       </c>
-      <c r="F22" s="6">
+      <c r="F22" s="5">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="G22" s="6">
         <v>3500</v>
       </c>
-      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
     </row>
-    <row r="23" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>46154</v>
       </c>
@@ -7663,12 +7845,16 @@
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A23,'[1]SO Warung'!$B:$B,B23,'[1]SO Warung'!$D:$D,C23)</f>
         <v>3</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F23" s="5">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="G23" s="6">
         <v>5500</v>
       </c>
-      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
     </row>
-    <row r="24" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>46154</v>
       </c>
@@ -7685,10 +7871,14 @@
         <f>SUMIFS('[1]SO Warung'!$I:$I,'[1]SO Warung'!$A:$A,A24,'[1]SO Warung'!$B:$B,B24,'[1]SO Warung'!$D:$D,C24)</f>
         <v>1</v>
       </c>
-      <c r="F24" s="6">
+      <c r="F24" s="5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G24" s="6">
         <v>9000</v>
       </c>
-      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
